--- a/tools/planner-studio/app/seeds/Party.xlsx
+++ b/tools/planner-studio/app/seeds/Party.xlsx
@@ -73,62 +73,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Farmer_Party</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농부 덱</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Test_Party</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">테스트 덱</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UD_Frog_Archer;UD_Frog_Mage;UD_Frog_Priest;UD_Frog_Rogue</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TestPartyChieftain</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>